--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0063.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0063.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Điểm Giai Đoạn</t>
+          <t>Đạt 2.000 Điểm Sân Khấu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Điểm Giai Đoạn</t>
+          <t>Đạt 2.000 Điểm Sân Khấu</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Điểm Giai Đoạn</t>
+          <t>Đạt 2.000 Điểm Sân Khấu</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Điểm Giai Đoạn</t>
+          <t>Đạt 2.000 Điểm Sân Khấu</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Điểm Giai Đoạn</t>
+          <t>Đạt 2.000 Điểm Sân Khấu</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Enlarging Cargo</t>
+          <t>Mở rộng Khoang Hàng</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Enlarging Cargo</t>
+          <t>Mở rộng Khoang Hàng</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Ông Già và Cá Voi</t>
+          <t>Lão Già và Cá Voi</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Về Những Ảo Giác Của Ngàn Cánh Cổng</t>
+          <t>Về Ảo Ảnh Ngàn Cánh Cửa</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Fishing Rules</t>
+          <t>Quy Tắc Câu Cá</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Kết Cục Của Kẻ Sám Hối I</t>
+          <t>Kết Cục Của Kẻ Ăn Năn I</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối II</t>
+          <t>Kết Cục Của Kẻ Ăn Năn II</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối III</t>
+          <t>Hồi Kết của Kẻ Ăn Năn III</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối IV</t>
+          <t>Hồi Kết của Kẻ Ăn Năn IV</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối V</t>
+          <t>Hồi Kết của Kẻ Ăn Năn V</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Remnant Crystal</t>
+          <t>Pha Lê Tàn Tích</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Drifting Treasures</t>
+          <t>Kho báu Trôi dạt</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Drifting Treasures</t>
+          <t>Kho báu Trôi dạt</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Infinite Battle Simulation: Alertness</t>
+          <t>Mô Phỏng Chiến Đấu Vô Tận: Cảnh Giác</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Infinite Battle Simulation: Alertness</t>
+          <t>Mô Phỏng Chiến Đấu Vô Tận: Cảnh Giác</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Độ bền của Rachel</t>
+          <t>Độ Bền Rachel</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>About Infinite Battle Simulation II</t>
+          <t>Về Mô Phỏng Trận Chiến Vô Tận II</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Dreaming Deep</t>
+          <t>Giấc Mơ Sâu Thẳm</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Avinoleum Travel Atlas</t>
+          <t>Bản Đồ Du Hành Avinoleum</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Septimont Travel Atlas</t>
+          <t>Bản Đồ Du Hành Septimont</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Quà Tặng của Những Tràng Vỗ Tay</t>
+          <t>Quà tặng Tiếng Vỗ Tay</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Quà Tặng của Bản Giao Hưởng Vĩ Đại</t>
+          <t>Mộng Giao Hưởng Vĩ Đại</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Set Sail</t>
+          <t>Chiến Dịch Lollo: Khởi Hành</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Overflowing Picture Book</t>
+          <t>Sách Tranh Tràn</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Ragunna Weather Forecast</t>
+          <t>Dự Báo Thời Tiết Ragunna</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Sự kiện mới "Nếu Ngươi Nhìn Vào Vực Thẳm Của Giấc Mơ" đã mở!</t>
+          <t>Sự kiện mới "Nếu Ngươi Nhìn Vào Vực Thẳm Của Giấc Mơ" đã mở rồi!</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Quà Tặng của Nước Xanh</t>
+          <t>Quà tặng Nước Xanh</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Quà Tặng của Những Dòng Thủy Lặng</t>
+          <t>Quà Tặng Thủy Triều Lặng</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Saving Your Progress</t>
+          <t>Đang lưu tiến trình của bạn</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Surveillance Dataset</t>
+          <t>Bộ Dữ Liệu Giám Sát</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Titles</t>
+          <t>Danh Hiệu</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Đến cuối tuyến đường</t>
+          <t>Đến cuối con đường</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Earn Points</t>
+          <t>Nhận điểm</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Equipping Titles</t>
+          <t>Đang trang bị Danh Hiệu</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Dark Tide Vines: I</t>
+          <t>Dây Leo Thủy Triều Bóng Tối: I</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Dark Tide Vines: II</t>
+          <t>Dây Leo Thủy Triều Bóng Tối: II</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Remnant Spark</t>
+          <t>Tia Lửa Dư</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Các Tháp Obelisk và Xiềng Xích</t>
+          <t>Đài Kỷ Niệm và Xiềng Xích</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Gravity Calibrator</t>
+          <t>Bộ Điều Chỉnh Trọng Lực</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Yêu cầu Gondola</t>
+          <t>Đang gọi Gondola</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Gondola Ride</t>
+          <t>Chuyến đi Gondola</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Ace Wings</t>
+          <t>Đôi Cánh Phi Thường</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Boat Racing</t>
+          <t>Đua Thuyền</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Lối đi không hạn chế</t>
+          <t>Lối đi không giới hạn</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Bouncy Jellyfish</t>
+          <t>Sứa Nảy</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Ghosts Between Time</t>
+          <t>Những Ma Quỷ Giữa Thời Gian</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Vực Thẳm trong Bóng Tối</t>
+          <t>Hố Sâu trong Bóng Tối</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Overflowing Palette: Colorblocks</t>
+          <t>Bảng Màu Tràn: Khối Màu</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Flash Dodge</t>
+          <t>Né Tia Chớp</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Gravitation Flux</t>
+          <t>Dòng Chảy Hấp Dẫn</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Sketching</t>
+          <t>Phác họa</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Gondola Swim Up: Phaom</t>
+          <t>Lên Thuyền Gondola: Phaom</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Dream Patrol: Capitaneus</t>
+          <t>Tuần Tra Giấc Mơ: Capitaneus</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Purifying Statues</t>
+          <t>Tượng Tinh Luyện</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Dọn dẹp Đường Thủy</t>
+          <t>Thông dòng kênh nước</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Spark Throw</t>
+          <t>Ném Lấp Lánh</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Phía sau Cánh Cổng</t>
+          <t>Phía Sau Cánh Cổng</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Phá hủy Obelisk và Xiềng Xích</t>
+          <t>Phá Cột Đá và Xiềng Xích</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Changing Gravity Direction</t>
+          <t>Đang thay đổi hướng trọng lực</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Ánh Sáng Màu và Hướng Trọng Lực</t>
+          <t>Ánh Sáng Màu Sắc và Hướng Trọng Lực</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Lựa chọn Hướng Đi</t>
+          <t>Đang chọn hướng di chuyển</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Let's Go, Phaom</t>
+          <t>Đi thôi, Phaom</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Fixed Route</t>
+          <t>Lộ trình cố định</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Đuổi theo Tia Sáng trên Không</t>
+          <t>Đuổi theo những tia sáng lấp lánh trên không</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Đuổi theo Tia Sáng trên Mặt Nước</t>
+          <t>Đuổi theo những tia sáng lấp lánh trên mặt nước</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Switching Dimensions</t>
+          <t>Đang chuyển đổi chiều không gian</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Jellyfish Area</t>
+          <t>Khu Vực Sứa</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Bouncy Jellyfish</t>
+          <t>Sứa Nảy</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Chuyển đổi Không gian để Tấn công</t>
+          <t>Chuyển chiều tấn công</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Đẩy lùi Bóng Tối bằng Ánh Sáng</t>
+          <t>Ánh sáng xua tan bóng tối</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Locked Colors</t>
+          <t>Màu Khóa</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Avoiding Lightning Strikes</t>
+          <t>Tránh né những cú sét đánh</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Resonator Restrictions</t>
+          <t>Hạn chế đối với Resonator</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Vẽ họa tiết bằng Dấu chân</t>
+          <t>Vẽ Đường Viền Bằng Dấu Chân</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Lên Thủy Lộ</t>
+          <t>Lên Thủy Triều</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Sneak Attack</t>
+          <t>Tấn Công Bất Ngờ</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Sequence Mechanism</t>
+          <t>Cơ Chế Trình Tự</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Messenger Statue</t>
+          <t>Bức Tượng Sứ Giả</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Ventilation Tunnel</t>
+          <t>Hầm Thông Gió</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Spiral Column Drain</t>
+          <t>Ống Xả Cột Xoắn</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Sequence Mechanism</t>
+          <t>Cơ Chế Trình Tự</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Messenger Statue</t>
+          <t>Bức Tượng Sứ Giả</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Ventilation Tunnel</t>
+          <t>Hầm Thông Gió</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Spiral Column Drain</t>
+          <t>Ống Xả Cột Xoắn</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Shield Recovery</t>
+          <t>Khiên Phục Hồi</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Combo Effect</t>
+          <t>Hiệu Ứng Hồi Chiêu</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Shield Zone</t>
+          <t>Vùng Khiên</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Dominator Zone</t>
+          <t>Khu Vực Thống Trị</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Shield Recovery</t>
+          <t>Khiên Phục Hồi</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Combo Effect</t>
+          <t>Hiệu Ứng Hồi Chiêu</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Shield Zone</t>
+          <t>Vùng Khiên</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Dominator Zone</t>
+          <t>Khu Vực Thống Trị</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Cubie Derby: Warmup</t>
+          <t>Giải Đua Cubie: Khởi Động</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Conquer Abbowser Castle</t>
+          <t>Chinh phục Lâu đài Abbowser</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Cube Data Mô-đun</t>
+          <t>Mô-đun Dữ Liệu Khối</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Cube Data Mô-đun</t>
+          <t>Mô-đun Dữ Liệu Khối</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Cube Ability Mô-đun</t>
+          <t>Mô-đun Năng Lực Khối Lập Phương</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Cube Awakening Mô-đun</t>
+          <t>Mô-đun Thức Tỉnh Khối Lập Phương</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Obtaining Dice</t>
+          <t>Đang thu thập Xúc xắc</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Cube Encounter</t>
+          <t>Gặp Gỡ Khối</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Race Data</t>
+          <t>Dữ liệu đua</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Defeating Abbowser</t>
+          <t>Đánh bại Abbowser</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Ceremony Preparations</t>
+          <t>Chuẩn Bị Nghi Lễ</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Conquering Abbowser's Castle</t>
+          <t>Chinh phục Lâu Đài Abbowser</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Collecting Data Modules</t>
+          <t>Đang thu thập Mô-đun Dữ liệu</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Equipping Data Modules</t>
+          <t>Đang trang bị Mô-đun Dữ liệu</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Mô-đun Decompilation</t>
+          <t>Giải mã Mô-đun</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Nâng cấp Khối Lập Phương</t>
+          <t>Tăng cấp Khối Lập Phương</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Loại Mô-đun và Cách Nhận Mô-đun</t>
+          <t>Loại Mô-đun và Cách Nhận</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Ability Combos</t>
+          <t>Tổ Hợp Kỹ Năng</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Awakening Cubes</t>
+          <t>Khối Thức Tỉnh</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Procedure Hướng dẫn</t>
+          <t>Hướng dẫn Thao tác</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Race Schedule</t>
+          <t>Lịch đua</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Race Rules</t>
+          <t>Luật đua</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Finalization</t>
+          <t>Hoàn Thành</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Advancement Rules</t>
+          <t>Quy tắc thăng tiến</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Đến lúc Carnevale rồi!</t>
+          <t>Lễ hội Carnevale đến rồi!</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Basic Movement Rules</t>
+          <t>Quy Tắc Di Chuyển Cơ Bản</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Pad Stacking Rules</t>
+          <t>Quy Tắc Xếp Chồng Pad</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Quy tắc Hỗ trợ</t>
+          <t>Nguyên Tắc Hỗ Trợ</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Phần thưởng Hỗ trợ và Độ Phổ Biến</t>
+          <t>Ủng hộ và Phần thưởng Độ Phổ Biến</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Race Hướng dẫn</t>
+          <t>Hướng dẫn đua</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Tiến trình Vòng Đấu</t>
+          <t>Thăng Cấp Giai Đoạn</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Xem lại Trận Đấu và Tóm tắt Trận Đấu</t>
+          <t>Xem lại trận đấu và tóm tắt</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Quit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Dreaming Deep: Synergy Burst</t>
+          <t>Bùng Nổ Đồng Điệu: Giấc Mộng Sâu Thẳm</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Synergy</t>
+          <t>Cộng Hưởng</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Using Synergy Burst</t>
+          <t>Kích hoạt Đồng Bộ Bùng Nổ</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Synergy Burst Effect</t>
+          <t>Hiệu Ứng Cộng Hưởng Bùng Nổ</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Abbowser Castle</t>
+          <t>Lâu Đài Abbowser</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Chi Tiết Danh Hiệu</t>
+          <t>Chi tiết danh hiệu</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Hiển Thị Danh Hiệu</t>
+          <t>Hiển thị danh hiệu</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Cube, Cubic và Cubie</t>
+          <t>Khối, Khối Lập Phương và Cubie</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Diện mạo Echo</t>
+          <t>Thuộc Tính Echo</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Solaris New Voyage Celebration</t>
+          <t>Lễ kỷ niệm Hành trình Mới của Solaris</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Banner of Victory</t>
+          <t>Ngọn Cờ Chiến Thắng</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Major</t>
+          <t>Ngọn Cờ Chinh Phục: Cao</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Banner of Victory: End of Season</t>
+          <t>Ngọn Cờ Chiến Thắng: Kết Mùa</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Banner of Victory: End of Season</t>
+          <t>Ngọn Cờ Chiến Thắng: Kết Mùa</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Echo Types</t>
+          <t>Loại Echo</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Core Echo III</t>
+          <t>Tâm Ảnh Cốt Lõi III</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Core Echo I</t>
+          <t>Tiếng Vọng Cốt Lõi I</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Wuthering Exploration</t>
+          <t>Thám Hiểm Vực Gió</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Epic of the Blazing Sun</t>
+          <t>Sử Thi Mặt Trời Rực Cháy</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Bàn Thờ Hòa Âm</t>
+          <t>Bệ Phối Khí</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Quà Tặng Bình Minh Đến Gần</t>
+          <t>Quà tặng Bình Minh Đến Gần</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Quản lý Echo</t>
+          <t>Quản Lý Tiếng Vọng</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hiện Đã Có Sẵn</t>
+          <t>Đã Có Mặt</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Holy Summon: Retribution</t>
+          <t>Triệu Hồi Thánh: Trừng Phạt</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Orchestration: Operations</t>
+          <t>Điều phối: Thao tác</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Orchestration: Grapple</t>
+          <t>Điều phối: Khống chế</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Orchestration: Combat</t>
+          <t>Điều phối: Chiến đấu</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Micro Echo Brooders</t>
+          <t>Fabricatorium Vực Sâu: Micro Echo Brooders</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Power Controllers</t>
+          <t>Fabricatorium Vực Sâu: Bộ Điều Khiển Năng Lượng</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Bàn Thờ Hòa Âm</t>
+          <t>Bệ Phối Khí</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Cưỡi Dòng Nước</t>
+          <t>Cưỡi Dòng Chảy</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Energy Pipes</t>
+          <t>Fabricatorium Vực Sâu: Đường Ống Năng Lượng</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Breakers</t>
+          <t>Fabricatorium Vực Sâu: Bộ Phá Hỏng</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Prayer Rite</t>
+          <t>Nghi Lễ Cầu Nguyện</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Triptych Chest</t>
+          <t>Rương Ba Mảnh</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Holy Summon: Retribution I</t>
+          <t>Triệu Hồi Thánh: Trừng Phạt I</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Holy Summon: Retribution II</t>
+          <t>Triệu Hồi Thánh: Trừng Phạt II</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Orchestration Skill</t>
+          <t>Kỹ Năng Phối Khí</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Orchestration Energy Restoration</t>
+          <t>Hồi Phục Năng Lượng Phối Khí</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Orchestration: Grapple</t>
+          <t>Điều phối: Khống chế</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Orchestration: Attacking Enemies</t>
+          <t>Điều phối: Tấn công kẻ địch</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Orchestration: Enemy State</t>
+          <t>Điều phối: Trạng thái kẻ địch</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Micro Echo Brooders</t>
+          <t>Fabricatorium Vực Sâu: Micro Echo Brooders</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Power Controllers</t>
+          <t>Fabricatorium Vực Sâu: Bộ Điều Khiển Năng Lượng</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Music Stand</t>
+          <t>Giá Đỡ Bản Nhạc</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Polyphone Orchestration</t>
+          <t>Dàn Hòa Âm Đa Âm</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Completing Orchestration</t>
+          <t>Hoàn Thành Dàn Nhạc</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Nhiều Nốt Nhạc và Điểm Kết Thúc Của Chúng</t>
+          <t>Nhiều Nốt Nhạc và Điểm Kết của chúng</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Đi Vào Dòng Nước</t>
+          <t>Đi vào Dòng Chảy</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Kiểm Soát Dòng Nước</t>
+          <t>Điều khiển Dòng Chảy</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Energy Pipes</t>
+          <t>Fabricatorium Vực Sâu: Đường Ống Năng Lượng</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Fabricatorium of the Deep: Breakers</t>
+          <t>Fabricatorium Vực Sâu: Bộ Phá Hỏng</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Prayer Rite</t>
+          <t>Nghi Lễ Cầu Nguyện</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Triptych Chest</t>
+          <t>Rương Ba Mảnh</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Các Giai Đoạn và Ngày Tháng</t>
+          <t>Pha và Ngày</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Dreamland Echoes và Dream Block</t>
+          <t>Tiếng Vọng Giấc Mơ và Khối Giấc Mơ</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Dreamland Echoes and Yield</t>
+          <t>Hồi Âm và Nơi Quy Hạ Giấc Mơ</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Giấc Mơ Phân Tầng</t>
+          <t>Hướng Dẫn Giấc Mộng Phân Tầng</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Giấc Mơ Nuốt Chửng</t>
+          <t>Hướng Dẫn Giấc Mộng Nuốt Chửng</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Giấc Mơ Trao Đổi</t>
+          <t>Hướng Dẫn Giấc Mộng Trao Đổi</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Giấc Mơ Hòa Nhập</t>
+          <t>Hướng Dẫn Giấc Mộng Hòa Nhập</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Gradation Guide</t>
+          <t>Hướng Dẫn Phân Cấp</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Devouring Guide</t>
+          <t>Hướng dẫn Nuốt chửng</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Giấc Mơ Trao Đổi</t>
+          <t>Hướng Dẫn Giấc Mộng Trao Đổi</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Giấc Mơ Hòa Nhập</t>
+          <t>Hướng Dẫn Giấc Mộng Hòa Nhập</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Giấc Mơ Kết Nối</t>
+          <t>Hướng Dẫn Giấc Mộng Kết Nối</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Commons Guide</t>
+          <t>Hướng Dẫn Liên Lạc Cơ Bản</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Second Coming of Solaris (Ultra)</t>
+          <t>Sự Trở Lại Của Solaris (Cao Cấp)</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris</t>
+          <t>Thám Sát Âm Than: Lính Solaris</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris</t>
+          <t>Thám Sát Âm Than: Lính Solaris</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Rising Anew</t>
+          <t>Chiến Dịch Lollo: Trỗi Dậy Mới</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Kiểm Tra "Điềm Báo Số Mệnh"</t>
+          <t>Kiểm tra "Điềm Báo Định Mệnh"</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Anchoring Iuno</t>
+          <t>Neo Giữ Iuno</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Sử Dụng Iuno Để Hồi Phục</t>
+          <t>Sử dụng Iuno để Hồi Phục</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Đá Neo &amp; Đài Phun Neo</t>
+          <t>Đá Mỏ Neo &amp; Tháp Mỏ Neo</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Mysterious Light Dots</t>
+          <t>Những Đốm Sáng Bí Ẩn</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Waystones</t>
+          <t>Đá Dẫn Đường</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Unstable Rocks</t>
+          <t>Đá Bất Ổn</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Dreamscape Node - Sanguis Plateaus</t>
+          <t>Nút Giấc Mơ - Cao Nguyên Sanguis</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Confronting Augusta</t>
+          <t>Đối Mặt Augusta</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Inspecting "Omen"</t>
+          <t>Kiểm tra "Điềm Báo"</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Inspection Complete</t>
+          <t>Hoàn tất kiểm tra</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Anchoring - Holding Hands</t>
+          <t>Neo Giữ - Nắm Tay Nhau</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Interrupting Anchoring</t>
+          <t>Đang ngắt Neo Đậu</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Sử Dụng Iuno Để Hồi Phục</t>
+          <t>Sử dụng Iuno để Hồi Phục</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Đá Neo &amp; Đài Phun Neo</t>
+          <t>Đá Mỏ Neo &amp; Tháp Mỏ Neo</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mysterious Light Dots</t>
+          <t>Những Đốm Sáng Bí Ẩn</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Hollow Figure</t>
+          <t>Hình Nhân Rỗng</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Waystones</t>
+          <t>Đá Dẫn Đường</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Unstable Rocks</t>
+          <t>Đá Bất Ổn</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Dreamscape Node - Sanguis Plateaus</t>
+          <t>Nút Giấc Mơ - Cao Nguyên Sanguis</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Confronting Augusta</t>
+          <t>Đối Mặt Augusta</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tidal Defense Simulator - Deathtrap Mode</t>
+          <t>Mô phỏng Phòng thủ Thủy Triều - Chế độ Bẫy Chết</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Terrain Change</t>
+          <t>Thay Đổi Địa Hình</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Mô Phỏng Phòng Thủ Thủy Triều - Cửa Hàng KU-Money</t>
+          <t>Mô phỏng Phòng thủ Thủy Triều - Cửa hàng KU-Money</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Analyzing Traces</t>
+          <t>Phân Tích Dấu Vết</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Building Up Defenses</t>
+          <t>Đang Củng Cố Phòng Thủ</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Combat Machines</t>
+          <t>Máy Chiến Đấu</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Defending Matrix</t>
+          <t>Ma Trận Phòng Thủ</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Incoming Tacet Discords</t>
+          <t>Tacet Discord sắp xuất hiện!</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Rating Stars</t>
+          <t>Sao đánh giá</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Tactic Selection</t>
+          <t>Lựa Chọn Chiến Thuật</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Total Defense Test</t>
+          <t>Kiểm tra Phòng Ngự Tổng</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Terrain Change</t>
+          <t>Thay Đổi Địa Hình</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Cửa Hàng Mở</t>
+          <t>Mở Cửa Hàng</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Sử Dụng Vật Phẩm</t>
+          <t>Sử dụng vật phẩm</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Switching Vật phẩm</t>
+          <t>Đang chuyển đổi vật phẩm</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Connecting Samples</t>
+          <t>Đang kết nối Mẫu Dữ Liệu</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Anchoring Samples</t>
+          <t>Đang neo giữ Mẫu</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hoàn Thành Phân Tích</t>
+          <t>Đang Hoàn Thành Phân Tích</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Terminal Swap</t>
+          <t>Hoán Đổi Thiết Bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Chế độ護 mắt</t>
+          <t>Chế Độ Chăm Sóc Mắt</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Cần khởi động lại game để cài đặt Ray Tracing có hiệu lực</t>
+          <t>Cần khởi động lại trò chơi để cài đặt Dò Tia có hiệu lực</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Removing Shields</t>
+          <t>Đang phá vỡ Khiên bảo vệ</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Terrain Kills</t>
+          <t>Tiêu Diệt Bằng Địa Hình</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Passive - Fortified</t>
+          <t>Thụ Động - Củng Cố</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Domain - Disable</t>
+          <t>Tổ Tacet - Vô Hiệu Hóa</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Passive - Invisibility</t>
+          <t>Thụ Động - Tàng Hình</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Domain - Barrier</t>
+          <t>Tổ Tacet - Rào Chắn</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Deathsound - Contamination</t>
+          <t>Âm Tử - Ô Nhiễm</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Removing Shields</t>
+          <t>Đang phá vỡ Khiên bảo vệ</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Terrain Kills</t>
+          <t>Tiêu Diệt Bằng Địa Hình</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Passive - Fortified</t>
+          <t>Thụ Động - Củng Cố</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Domain - Disable</t>
+          <t>Tổ Tacet - Vô Hiệu Hóa</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Passive - Invisibility</t>
+          <t>Thụ Động - Tàng Hình</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Domain - Barrier</t>
+          <t>Tổ Tacet - Rào Chắn</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Aftertune - Contamination</t>
+          <t>Giai Điệu Dư Âm - Ô Nhiễm</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Clearing Frequency Contamination</t>
+          <t>Dọn dẹp Ô Nhiễm Tần Số</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Dấu Ấn Hoang Dã</t>
+          <t>Dấu Vết Hoang Dã</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Matrix Durability</t>
+          <t>Độ Bền Ma Trận</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Matrix Durability</t>
+          <t>Độ Bền Ma Trận</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Vị cứu tinh băng giá</t>
+          <t>Chiến Dịch Lollo: Vị Cứu Tinh Băng Giá</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Overwatch Protocol</t>
+          <t>Giao thức Giám sát</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Cỗ Máy Chiến Đấu &amp; Vũ Khí của KU-Roro</t>
+          <t>Máy Chiến Đấu &amp; Vũ Khí KU-Roro</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Mở Khóa Qua Việc Nhận Vật Phẩm</t>
+          <t>Mở khóa bằng cách thu thập vật phẩm</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Đang Bị Khóa</t>
+          <t>Nhiệm vụ bị khóa</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Đang Bị Khóa</t>
+          <t>Nhiệm vụ bị khóa</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Đang Bị Khóa</t>
+          <t>Nhiệm vụ bị khóa</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Septimont Weather Forecast</t>
+          <t>Dự Báo Thời Tiết Septimont</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Quà Tặng Từ Kẻ Lang Thang Mặt Trăng</t>
+          <t>Quà Tặng Kẻ Lang Thang Trăng</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>New Update Highlight</t>
+          <t>Điểm nổi bật của bản cập nhật mới</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Resonator có thể sử dụng Kỹ Năng Chủ Động và Dash</t>
+          <t>Resonator có thể sử dụng Kỹ Năng Chủ Động và Tấn Công Nhanh.</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Terminal Swap</t>
+          <t>Hoán Đổi Thiết Bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Switching Terminals</t>
+          <t>Đang chuyển đổi Thiết bị đầu cuối</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>World Crossing: Distortion</t>
+          <t>Vượt Thế: Biến dạng</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Tidespawn: Paradise Shelter</t>
+          <t>Tidespawn: Nơi Trú Ẩn Thiên Đường</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>World Crossing: Battle</t>
+          <t>Vượt Thế: Chiến đấu</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Way Out</t>
+          <t>Lối Thoát</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Beholder's Vision</t>
+          <t>Thị Giác của Người Quan Sát</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Vượt Giới: Tách Rời và Chuyển Đổi</t>
+          <t>Vượt Thế: Tách rời và chuyển đổi</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Paradise Shelter</t>
+          <t>Nơi Trú Ẩn Thiên Đường</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Dark Tide's Influence</t>
+          <t>Ảnh Hưởng của Dòng Hắc Triều</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Breaking Paradise Shelter</t>
+          <t>Phá Nơi Ẩn Náu Thiên Đường</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Sự Bảo Vệ Từ Cassette</t>
+          <t>Bảo vệ bởi Cassette</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Khoảnh Khắc Chuyển Đổi</t>
+          <t>Khoảnh Khắc Chuyển Giao</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Beholder's Vision</t>
+          <t>Thị Giác của Người Quan Sát</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Feather Blade</t>
+          <t>Lưỡi Kiếm Lông Vũ</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Tearing Apart</t>
+          <t>Xé Nát</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Hunting Hour</t>
+          <t>Giờ Săn Mồi</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Sub-Memory Zone</t>
+          <t>Khu Vực Tiềm Thức Phụ</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris</t>
+          <t>Thám Sát Âm Than: Lính Solaris</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris - Vũ Khí</t>
+          <t>Thám Sát Âm Than: Lính Solaris - Vũ Khí</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris - Rương</t>
+          <t>Thám Sát Âm Than: Lính Solaris - Rương</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris - Chế Độ Helltide</t>
+          <t>Thám Sát Âm Than: Lính Solaris - Chế Độ Hỏa Ngục</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris - Vượt Qua Một Đợt</t>
+          <t>Thám Sát Âm Than: Lính Solaris - Dọn Sóng</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris - Tinh Anh</t>
+          <t>Thám Sát Âm Than: Lính Solaris - Đối Thủ Mạnh</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris - Nhặt Đồ</t>
+          <t>Thám Sát Âm Than: Lính Solaris - Nhặt Đồ</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Freeze Frame Challenges</t>
+          <t>Thử Thách Định Hình</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Freeze Frame Challenges - Khó Mode</t>
+          <t>Thử Thách Định Hình - Chế Độ Khó</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Sub-Memory Zone</t>
+          <t>Khu Vực Tiềm Thức Phụ</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Drill Mode</t>
+          <t>Chế Độ Huấn Luyện</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Tactical View</t>
+          <t>Góc Nhìn Chiến Thuật</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Drill Process</t>
+          <t>Quá Trình Huấn Luyện</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>New Weapons</t>
+          <t>Vũ Khí Mới</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Weapon Evolution</t>
+          <t>Tiến Hóa Vũ Khí</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Special TD: Chests</t>
+          <t>Tổ Tacet Đặc Biệt: Rương</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Chế độ Helltide</t>
+          <t>Chế Độ Hắc Triều</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Vượt Qua Một Đợt</t>
+          <t>Dọn dẹp một đợt sóng</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Elites</t>
+          <t>Tinh nhuệ</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Picking Up Vật phẩm</t>
+          <t>Đang nhặt vật phẩm</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Chụp ảnh Shoot</t>
+          <t>Chụp Ảnh</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Thử Thách Freeze Frame - Chế Độ Dễ</t>
+          <t>Thử Thách Định Hình - Chế Độ Dễ</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Freeze Frame Challenges - Khó Mode</t>
+          <t>Thử Thách Định Hình - Chế Độ Khó</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Tactical Simulacra: Off Tune</t>
+          <t>Bản Sao Chiến Thuật: Lệch Tần</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Beyond the Waves: Lahai-Roi</t>
+          <t>Vượt Qua Những Con Sóng: Lahai-Roi</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Quà Tặng Tuần Lễ Tân Sinh Viên</t>
+          <t>Mộng Tuần Lễ Khai Sinh</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Phi Công</t>
+          <t>Ma trận Tốt Đôi: Phi Công</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Honami City: Loot</t>
+          <t>Thành phố Honami: Chiến lợi phẩm</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Honami City: Stability</t>
+          <t>Thành phố Honami: Sự Ổn Định</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Honami City: Namipon's Sparkling Water</t>
+          <t>Thành phố Honami: Nước Suối Lấp Lánh của Namipon</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Chuyện Lạ Ở Honami</t>
+          <t>Những Điều Kỳ Lạ Ở Honami</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Những Điều Kỳ Lạ Ở Honami: Vật Phẩm Bị Nhiễm Độc</t>
+          <t>Những Điều Kỳ Lạ Ở Honami: Vật Phẩm Nhiễm Độc</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Những Điều Kỳ Lạ Ở Honami: Khu Vực Tàn Tích Lament</t>
+          <t>Những Điều Kỳ Lạ Ở Honami: Khu Vực Tàn Tích Than Thở</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Những Điều Kỳ Lạ Ở Honami: Máy Bán Hàng Bị Nhiễm Độc</t>
+          <t>Những Điều Kỳ Lạ Ở Honami: Máy Bán Hàng Nhiễm Độc</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Honami City: Free Exploration</t>
+          <t>Thành phố Honami: Khám phá tự do</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Namipon Stickers</t>
+          <t>Sticker Namipon</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Obtaining Namipon Stickers</t>
+          <t>Đang thu thập Nhãn dán Namipon</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Ổn Định</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Mất Tất Cả Sự Ổn Định</t>
+          <t>Mất hết Độ Ổn Định</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Namipon's Sparkling Water</t>
+          <t>Nước Có Gas Của Namipon</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Namipon Sticker Set</t>
+          <t>Bộ sticker Namipon</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Contaminated Loot</t>
+          <t>Vật Phẩm Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Irideglow Contamination I</t>
+          <t>Nhiễm độc Irideglow I</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Irideglow Contamination II</t>
+          <t>Nhiễm độc Irideglow II</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Lament Residue Zones</t>
+          <t>Các Khu Vực Dư Lượng Âm Than</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Contaminated Capsule Machine</t>
+          <t>Máy Capsule Bị Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Namipon Telephone Booth</t>
+          <t>Buồng điện thoại Namipon</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Đặt Vé Tàu Con Thoi Namipon</t>
+          <t>Đang đặt vé tàu Namipon</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Honami City: Free Exploration</t>
+          <t>Thành phố Honami: Khám phá tự do</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Irideglow Portal</t>
+          <t>Cổng Irideglow</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Tunability</t>
+          <t>Độ Cộng Hưởng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Cấp Độ Lệch Nhịp</t>
+          <t>Cấp Độ Lệch Tần</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Synchronization</t>
+          <t>Hologram Chiến Thuật: Đồng Bộ Hóa</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Chuyện Lạ Ở Honami</t>
+          <t>Những Điều Kỳ Lạ Ở Honami</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Thư viện Collectibles</t>
+          <t>Bộ Sưu Tập Triển Lãm</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Enhance Resonator</t>
+          <t>Nâng cấp Resonator</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Combat Power</t>
+          <t>Sức Mạnh Chiến Đấu</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Exploration I - Honami City</t>
+          <t>Thám Hiểm I - Thành Phố Honami</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Exploration II - Neon Tower</t>
+          <t>Thám Hiểm II - Tháp Neon</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Trang Trí Quán Cà Phê</t>
+          <t>Trang trí quán cà phê</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Tìm Kiếm Những Namipon Mất Tích</t>
+          <t>Tìm những con Namipon bị mất tích</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Trạm tiếp tế</t>
+          <t>Trạm Cung Cấp</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Honami City: Namipon Lightbox</t>
+          <t>Thành phố Honami: Hộp đèn Namipon</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Honami City: Missing Namipons</t>
+          <t>Thành phố Honami: Namipon mất tích</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Honami City: Exclusive Namipon Stickers</t>
+          <t>Thành phố Honami: Bộ sticker Namipon độc quyền</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Honami City: Neon Tower</t>
+          <t>Thành phố Honami: Tháp Neon</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Namipon Lightbox</t>
+          <t>Đèn hộp Namipon</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Missing Namipon I</t>
+          <t>Thiếu Namipon I</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Missing Namipon II</t>
+          <t>Thiếu Namipon II</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Exclusive Namipon Sticker</t>
+          <t>Sticker Namipon Độc Quyền</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Honami City: Exploration</t>
+          <t>Thành phố Honami: Khám phá</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Investigating Anomalies</t>
+          <t>Đang điều tra các điểm dị thường...</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Free Exploration</t>
+          <t>Thám hiểm tự do</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>WavesLine</t>
+          <t>Đường Sóng</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Motorbike Progression</t>
+          <t>Nâng Cấp Xe Máy</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Giữ [Drift] trong khi di chuyển sang trái hoặc phải để drift</t>
+          <t>Giữ [Drift] khi di chuyển sang trái hoặc phải để trượt</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Lahai-Roi Pioneers</t>
+          <t>Những Tiên Phong Lahai-Roi</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Region Guide</t>
+          <t>Hướng dẫn khu vực</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Expansion Mô-đun Upgrades</t>
+          <t>Nâng cấp Mô-đun Mở rộng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Motorbike Modding Tasks</t>
+          <t>Nhiệm Vụ Nâng Cấp Xe Máy</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch tại Lahai-Roi</t>
+          <t>Tiêu diệt kẻ địch ở Lahai-Roi</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Echo Projector</t>
+          <t>Bộ Phát Tần Số</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Quà tặng của Tuyết Mềm</t>
+          <t>Quà Tặng Tuyết Mềm</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Resonators</t>
+          <t>Các Resonator Hỗ Trợ</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Sky Projection Array Control Mô-đun</t>
+          <t>Mô-đun Điều Khiển Mảng Chiếu Hình Trên Không</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Đẩy cần điều khiển để điều chỉnh hướng xe máy thám hiểm</t>
+          <t>Gạt cần để điều khiển hướng xe thám hiểm</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Giữ Boost để tăng tốc</t>
+          <t>Giữ Boost để tăng tốc độ di chuyển.</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Radio xe máy và Chế độ điện ảnh</t>
+          <t>Radio Xe Máy &amp; Chế Độ Cinematic</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Autopilot Mode</t>
+          <t>Chế Độ Tự Lái</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Void Storm Zone</t>
+          <t>Khu Vực Bão Hư Không</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Phần thưởng khu vực</t>
+          <t>Phần thưởng Khu</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Motorbike Features</t>
+          <t>Tính Năng Xe Máy</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Triệu hồi xe máy</t>
+          <t>Đang triệu hồi Xe Máy</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Những điều cần lưu ý khi lái xe máy</t>
+          <t>Những Lưu Ý Khi Lái Xe Máy</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Cinematic Mode</t>
+          <t>Chế Độ Điện Ảnh</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Autopilot Mode</t>
+          <t>Chế Độ Tự Lái</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Navigation Tracking</t>
+          <t>Theo dõi Định vị</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Autopilot Controls</t>
+          <t>Điều Khiển Tự Lái</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Free Autopilot</t>
+          <t>Tự lái miễn phí</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Sử dụng nút tương tác để tung chiêu Tune Break</t>
+          <t>Nhấn nút tương tác để thi triển Tune Break</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Sử dụng nút tương tác để tung chiêu Tune Break</t>
+          <t>Nhấn nút tương tác để thi triển Tune Break</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Kích hoạt Bộ Tạo Lộ Trình</t>
+          <t>Kích hoạt Bộ Xây dựng Lộ trình</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Rebuild Materials</t>
+          <t>Vật liệu tái thiết</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Reconstruction Gain</t>
+          <t>Lợi ích tái cấu trúc</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Reconstruction Navigation</t>
+          <t>Điều Hướng Tái Cấu Trúc</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Tiếp tục công cuộc tái thiết</t>
+          <t>Tiếp tục công cuộc tái thiết.</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Hỗ trợ dự án tái thiết Spacetrek Observatory</t>
+          <t>Hỗ trợ dự án tái thiết Đài Quan sát Spacetrek</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Route Network Reconstruction</t>
+          <t>Tái Thiết Mạng Lưới Tuyến Đường</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Tunability</t>
+          <t>Độ Cộng Hưởng</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Mức độ Off-Tune</t>
+          <t>Cấp Độ Lệch Tần</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Tune Disruption</t>
+          <t>Rối Loạn Tần Số</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Mistune: Immunity</t>
+          <t>Mistune: Miễn Dịch</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
